--- a/NSE/Cash segment/nse_daily.xlsx
+++ b/NSE/Cash segment/nse_daily.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1455"/>
+  <dimension ref="A1:E1456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -28068,6 +28068,25 @@
         <v>89436.36</v>
       </c>
     </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>17-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1456" t="n">
+        <v>3255</v>
+      </c>
+      <c r="C1456" t="n">
+        <v>29479854</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>45671.12</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>95690.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NSE/Cash segment/nse_daily.xlsx
+++ b/NSE/Cash segment/nse_daily.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1456"/>
+  <dimension ref="A1:E1458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -24848,13 +24848,13 @@
         <v>2992</v>
       </c>
       <c r="C1286" t="n">
-        <v>2992</v>
+        <v>35010629</v>
       </c>
       <c r="D1286" t="n">
-        <v>35010629</v>
+        <v>47810.3</v>
       </c>
       <c r="E1286" t="n">
-        <v>47810.3</v>
+        <v>104981.8</v>
       </c>
     </row>
     <row r="1287">
@@ -28085,6 +28085,44 @@
       </c>
       <c r="E1456" t="n">
         <v>95690.63</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>18-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1457" t="n">
+        <v>3285</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>28396581</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>45521.93</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>92768.41</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1458" t="n">
+        <v>3254</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>28073528</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>37440.37</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>93811.52</v>
       </c>
     </row>
   </sheetData>

--- a/NSE/Cash segment/nse_daily.xlsx
+++ b/NSE/Cash segment/nse_daily.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1458"/>
+  <dimension ref="A1:E1459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -28125,6 +28125,25 @@
         <v>93811.52</v>
       </c>
     </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>20-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1459" t="n">
+        <v>3255</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>27170013</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>35098.33</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>92643.78999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NSE/Cash segment/nse_daily.xlsx
+++ b/NSE/Cash segment/nse_daily.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1459"/>
+  <dimension ref="A1:E1469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -28144,6 +28144,196 @@
         <v>92643.78999999999</v>
       </c>
     </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>23-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1460" t="n">
+        <v>3288</v>
+      </c>
+      <c r="C1460" t="n">
+        <v>31051512</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>49124.95</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>101052.48</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>24-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1461" t="n">
+        <v>3279</v>
+      </c>
+      <c r="C1461" t="n">
+        <v>32472168</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>49224.9</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>113004.6</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>25-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1462" t="n">
+        <v>3291</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>31214021</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>41055.84</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>108503.78</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>26-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1463" t="n">
+        <v>3265</v>
+      </c>
+      <c r="C1463" t="n">
+        <v>30748283</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>45182.34</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>108665.76</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>27-Feb-2026</t>
+        </is>
+      </c>
+      <c r="B1464" t="n">
+        <v>3243</v>
+      </c>
+      <c r="C1464" t="n">
+        <v>34269344</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>54541.88</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>144962.74</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>02-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1465" t="n">
+        <v>3304</v>
+      </c>
+      <c r="C1465" t="n">
+        <v>42815926</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>61870.02</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>135372.72</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>04-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1466" t="n">
+        <v>3346</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>45563913</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>58557.38</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>140954.35</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>05-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1467" t="n">
+        <v>3341</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>37647908</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>49299.99</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>124022.64</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>06-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1468" t="n">
+        <v>3303</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>33503488</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>40833.39</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>110554.19</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>09-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1469" t="n">
+        <v>3379</v>
+      </c>
+      <c r="C1469" t="n">
+        <v>40126768</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>47095.97</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>116595.57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NSE/Cash segment/nse_daily.xlsx
+++ b/NSE/Cash segment/nse_daily.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1469"/>
+  <dimension ref="A1:E1471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -28334,6 +28334,44 @@
         <v>116595.57</v>
       </c>
     </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>10-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1470" t="n">
+        <v>3312</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>35185542</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>44557.14</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>114279.83</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1471" t="n">
+        <v>3306</v>
+      </c>
+      <c r="C1471" t="n">
+        <v>36099737</v>
+      </c>
+      <c r="D1471" t="n">
+        <v>43425.85</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>110325.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NSE/Cash segment/nse_daily.xlsx
+++ b/NSE/Cash segment/nse_daily.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1471"/>
+  <dimension ref="A1:E1483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -28372,6 +28372,234 @@
         <v>110325.31</v>
       </c>
     </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>12-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1472" t="n">
+        <v>3313</v>
+      </c>
+      <c r="C1472" t="n">
+        <v>40117363</v>
+      </c>
+      <c r="D1472" t="n">
+        <v>50348.45</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>123891.41</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>13-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1473" t="n">
+        <v>3325</v>
+      </c>
+      <c r="C1473" t="n">
+        <v>41354345</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>52708.04</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>121547.53</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>16-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1474" t="n">
+        <v>3378</v>
+      </c>
+      <c r="C1474" t="n">
+        <v>41358036</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>54879.88</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>124924.28</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1475" t="n">
+        <v>3331</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>35943126</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>45017.62</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>107083.39</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>18-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1476" t="n">
+        <v>3340</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>35542598</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>49697.41</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>107541.69</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>19-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1477" t="n">
+        <v>3312</v>
+      </c>
+      <c r="C1477" t="n">
+        <v>36240698</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>55121.36</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>112093.07</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>20-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1478" t="n">
+        <v>3328</v>
+      </c>
+      <c r="C1478" t="n">
+        <v>37214734</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>58650.75</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>140228.16</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>23-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1479" t="n">
+        <v>3427</v>
+      </c>
+      <c r="C1479" t="n">
+        <v>46078096</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>67223.78</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>130437.72</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>24-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1480" t="n">
+        <v>3374</v>
+      </c>
+      <c r="C1480" t="n">
+        <v>39718597</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>56339.25</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>128067.97</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1481" t="n">
+        <v>3373</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>39729955</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>54749.96</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>126314.43</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>27-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1482" t="n">
+        <v>3393</v>
+      </c>
+      <c r="C1482" t="n">
+        <v>48815341</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>66583.13</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>157107.82</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>30-Mar-2026</t>
+        </is>
+      </c>
+      <c r="B1483" t="n">
+        <v>3418</v>
+      </c>
+      <c r="C1483" t="n">
+        <v>45481735</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>64740.61</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>146863.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NSE/Cash segment/nse_daily.xlsx
+++ b/NSE/Cash segment/nse_daily.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1483"/>
+  <dimension ref="A1:E1487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -28600,6 +28600,82 @@
         <v>146863.59</v>
       </c>
     </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1484" t="n">
+        <v>3326</v>
+      </c>
+      <c r="C1484" t="n">
+        <v>38449296</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>54175.39</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>127242.24</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>02-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1485" t="n">
+        <v>3313</v>
+      </c>
+      <c r="C1485" t="n">
+        <v>37187328</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>54919.87</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>117090.06</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>06-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1486" t="n">
+        <v>3350</v>
+      </c>
+      <c r="C1486" t="n">
+        <v>36150085</v>
+      </c>
+      <c r="D1486" t="n">
+        <v>51368.7</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>116115.39</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>07-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1487" t="n">
+        <v>3317</v>
+      </c>
+      <c r="C1487" t="n">
+        <v>32575574</v>
+      </c>
+      <c r="D1487" t="n">
+        <v>42189.67</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>110461.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NSE/Cash segment/nse_daily.xlsx
+++ b/NSE/Cash segment/nse_daily.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1487"/>
+  <dimension ref="A1:E1509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1">
@@ -28676,6 +28676,424 @@
         <v>110461.9</v>
       </c>
     </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>08-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1488" t="n">
+        <v>3376</v>
+      </c>
+      <c r="C1488" t="n">
+        <v>43017735</v>
+      </c>
+      <c r="D1488" t="n">
+        <v>68317.09</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>165926.19</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1489" t="n">
+        <v>3326</v>
+      </c>
+      <c r="C1489" t="n">
+        <v>37488343</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>56899.3</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>133363.65</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>10-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1490" t="n">
+        <v>3349</v>
+      </c>
+      <c r="C1490" t="n">
+        <v>36072250</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>59827.14</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>131731.07</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>13-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1491" t="n">
+        <v>3329</v>
+      </c>
+      <c r="C1491" t="n">
+        <v>36070752</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>54076.63</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>129987.55</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>15-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1492" t="n">
+        <v>3367</v>
+      </c>
+      <c r="C1492" t="n">
+        <v>40089770</v>
+      </c>
+      <c r="D1492" t="n">
+        <v>60364.92</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>145330.45</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>16-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1493" t="n">
+        <v>3330</v>
+      </c>
+      <c r="C1493" t="n">
+        <v>39432979</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>58095.58</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>152709.34</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>17-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1494" t="n">
+        <v>3356</v>
+      </c>
+      <c r="C1494" t="n">
+        <v>39832018</v>
+      </c>
+      <c r="D1494" t="n">
+        <v>61629.48</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>151704.89</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1495" t="n">
+        <v>3430</v>
+      </c>
+      <c r="C1495" t="n">
+        <v>37552407</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>53500.2</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>129979.03</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>21-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1496" t="n">
+        <v>3440</v>
+      </c>
+      <c r="C1496" t="n">
+        <v>34128937</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>47634.18</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>127825.49</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1497" t="n">
+        <v>3402</v>
+      </c>
+      <c r="C1497" t="n">
+        <v>37122141</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>51529.13</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>137113.19</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1498" t="n">
+        <v>3400</v>
+      </c>
+      <c r="C1498" t="n">
+        <v>36379344</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>48859.28</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>135481.36</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>24-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1499" t="n">
+        <v>3403</v>
+      </c>
+      <c r="C1499" t="n">
+        <v>36545589</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>44965.11</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>130943.28</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>27-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1500" t="n">
+        <v>3451</v>
+      </c>
+      <c r="C1500" t="n">
+        <v>36942015</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>46173.99</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>131255.64</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>28-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1501" t="n">
+        <v>3383</v>
+      </c>
+      <c r="C1501" t="n">
+        <v>35565228</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>52059.82</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>138087.33</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>29-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1502" t="n">
+        <v>3399</v>
+      </c>
+      <c r="C1502" t="n">
+        <v>37113971</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>51420.19</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>139280.09</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>30-Apr-2026</t>
+        </is>
+      </c>
+      <c r="B1503" t="n">
+        <v>3374</v>
+      </c>
+      <c r="C1503" t="n">
+        <v>39483279</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>47306.19</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>142553.51</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B1504" t="n">
+        <v>3435</v>
+      </c>
+      <c r="C1504" t="n">
+        <v>40989517</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>55859.45</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>136831.09</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B1505" t="n">
+        <v>3397</v>
+      </c>
+      <c r="C1505" t="n">
+        <v>37251678</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>49392.77</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>128629.18</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B1506" t="n">
+        <v>3379</v>
+      </c>
+      <c r="C1506" t="n">
+        <v>40907138</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>58525.08</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>151681.61</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B1507" t="n">
+        <v>3397</v>
+      </c>
+      <c r="C1507" t="n">
+        <v>41857938</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>55738.41</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>153598.59</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B1508" t="n">
+        <v>3393</v>
+      </c>
+      <c r="C1508" t="n">
+        <v>41122363</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>51591.02</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>147669.21</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B1509" t="n">
+        <v>3427</v>
+      </c>
+      <c r="C1509" t="n">
+        <v>43253759</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>66521.49000000001</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>138987.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
